--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2297">
   <si>
     <t>en</t>
   </si>
@@ -6475,418 +6475,421 @@
     <t>扭曲仙境</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>超杀</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>海之子 - 当他们哭泣</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>地下物语</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>暗黑 AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>暗黑黄</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>宇宙符号</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>向上</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>城市野生动物</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>情人节</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>香草（已删除）</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>香草块</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>香草食品</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>香草头盔</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>香草物品</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>香草暴徒</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>金库猎人</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>蔬菜</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>车辆</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>维京人</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>村民</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>村民（沙漠）</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>村民（丛林）</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>村民（平原）</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>村民（草原）</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>村民（苔原雪原）</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>村民（沼泽）</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>村民（泰加针叶林）</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>虚拟优酷</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>虚拟歌手</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>伏特龙</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>若夫</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>行尸走肉</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>华莱士与格罗米特</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>世界大战</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>魔兽争霸</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>战锤</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>勇士猫</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>我们熊熊</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>我们是快乐的少数</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>天气</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>欢迎回家</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>这是谁？</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>野性更新</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>火之翼</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>小熊维尼</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>冬天</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>巫师</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>奇妙仙境</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>木头</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>羊毛</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>工作安全帽</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>无敌破坏王</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>X 战警</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>荡妇模拟器</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>黄色潜水艇</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>横行霸道</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>年轻</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>游戏王</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>梦幻妮琪</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>零之月</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>零之翼</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>黄道十二宫</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>僵尸</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>僵尸（香草）</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>超杀</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>海之子 - 当他们哭泣</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>地下物语</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>暗黑 AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>暗黑黄</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>宇宙符号</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>向上</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>城市野生动物</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>情人节</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>香草（已删除）</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>香草块</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>香草食品</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>香草头盔</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>香草物品</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>香草暴徒</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>金库猎人</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>蔬菜</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>车辆</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>维京人</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>村民</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>村民（沙漠）</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>村民（丛林）</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>村民（平原）</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>村民（草原）</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>村民（苔原雪原）</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>村民（沼泽）</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>村民（泰加针叶林）</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>虚拟优酷</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>虚拟歌手</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>伏特龙</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>若夫</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>行尸走肉</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>华莱士与格罗米特</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>世界大战</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>魔兽争霸</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>战锤</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>勇士猫</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>我们熊熊</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>我们是快乐的少数</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>天气</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>欢迎回家</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>这是谁？</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>野性更新</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>火之翼</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>小熊维尼</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>冬天</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>巫师</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>奇妙仙境</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>木头</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>羊毛</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>工作安全帽</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>无敌破坏王</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>X 战警</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>荡妇模拟器</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>黄色潜水艇</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>横行霸道</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>年轻</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>游戏王</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>梦幻妮琪</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>零之月</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>零之翼</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>黄道十二宫</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>僵尸</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>僵尸（香草）</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -7251,7 +7254,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16663,27 +16666,35 @@
         <v>2290</v>
       </c>
       <c r="B1176" t="s">
-        <v>2291</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2292</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1178" t="s">
         <v>2294</v>
       </c>
-      <c r="B1178" t="s">
+    </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
         <v>2295</v>
       </c>
+      <c r="B1179" t="s">
+        <v>2296</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2298">
   <si>
     <t>en</t>
   </si>
@@ -4712,6 +4712,9 @@
   </si>
   <si>
     <t>开源对象</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -7254,7 +7257,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13650,303 +13653,303 @@
         <v>1566</v>
       </c>
       <c r="B799" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B800" t="s">
         <v>1568</v>
-      </c>
-      <c r="B800" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B801" t="s">
         <v>1570</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B802" t="s">
         <v>1572</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B803" t="s">
         <v>1574</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B804" t="s">
         <v>1576</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B805" t="s">
         <v>1578</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B806" t="s">
         <v>1580</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B807" t="s">
         <v>1582</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1583</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B808" t="s">
         <v>1584</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B809" t="s">
         <v>1586</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B810" t="s">
         <v>1588</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B811" t="s">
         <v>1590</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B812" t="s">
         <v>1592</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B813" t="s">
         <v>1594</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1595</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B814" t="s">
         <v>1596</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B815" t="s">
         <v>1598</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B816" t="s">
         <v>1600</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B817" t="s">
         <v>1602</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B818" t="s">
         <v>1604</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B819" t="s">
         <v>1606</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B820" t="s">
         <v>1608</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B821" t="s">
         <v>1610</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B822" t="s">
         <v>1612</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B823" t="s">
         <v>1614</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B824" t="s">
         <v>1616</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B825" t="s">
         <v>1618</v>
-      </c>
-      <c r="B825" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B826" t="s">
         <v>1620</v>
-      </c>
-      <c r="B826" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B827" t="s">
         <v>1622</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B828" t="s">
         <v>1624</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B829" t="s">
         <v>1626</v>
-      </c>
-      <c r="B829" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B830" t="s">
         <v>1628</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B831" t="s">
         <v>1630</v>
-      </c>
-      <c r="B831" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B832" t="s">
         <v>1632</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B833" t="s">
         <v>1634</v>
-      </c>
-      <c r="B833" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B834" t="s">
         <v>1636</v>
-      </c>
-      <c r="B834" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B835" t="s">
         <v>1638</v>
-      </c>
-      <c r="B835" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B836" t="s">
         <v>1640</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="837" spans="1:2">
@@ -13954,63 +13957,63 @@
         <v>1641</v>
       </c>
       <c r="B837" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B838" t="s">
         <v>1643</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B839" t="s">
         <v>1645</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B840" t="s">
         <v>1647</v>
-      </c>
-      <c r="B840" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B841" t="s">
         <v>1649</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B842" t="s">
         <v>1651</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B843" t="s">
         <v>1653</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B844" t="s">
         <v>1655</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -14018,7 +14021,7 @@
         <v>1656</v>
       </c>
       <c r="B845" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -14026,132 +14029,132 @@
         <v>1657</v>
       </c>
       <c r="B846" t="s">
-        <v>1658</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B847" t="s">
         <v>1659</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B848" t="s">
         <v>1661</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B849" t="s">
         <v>1663</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B850" t="s">
         <v>1665</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B851" t="s">
         <v>1667</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B852" t="s">
         <v>1669</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B853" t="s">
         <v>1671</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B854" t="s">
         <v>1673</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B855" t="s">
         <v>1675</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1676</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B856" t="s">
         <v>1677</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B857" t="s">
         <v>1679</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B858" t="s">
         <v>1681</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B859" t="s">
         <v>1683</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1684</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B860" t="s">
         <v>1685</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B861" t="s">
         <v>1687</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B862" t="s">
         <v>1689</v>
@@ -14178,116 +14181,116 @@
         <v>1692</v>
       </c>
       <c r="B865" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B866" t="s">
         <v>1694</v>
-      </c>
-      <c r="B866" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B867" t="s">
         <v>1696</v>
-      </c>
-      <c r="B867" t="s">
-        <v>1697</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B868" t="s">
         <v>1698</v>
-      </c>
-      <c r="B868" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B869" t="s">
         <v>1700</v>
-      </c>
-      <c r="B869" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B870" t="s">
         <v>1702</v>
-      </c>
-      <c r="B870" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B871" t="s">
         <v>1704</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B872" t="s">
         <v>1706</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B873" t="s">
         <v>1708</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B874" t="s">
         <v>1710</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1711</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B875" t="s">
         <v>1712</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B876" t="s">
         <v>1714</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1715</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B877" t="s">
         <v>1716</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B878" t="s">
         <v>1718</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B879" t="s">
         <v>1720</v>
@@ -14298,44 +14301,44 @@
         <v>1721</v>
       </c>
       <c r="B880" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B881" t="s">
         <v>1723</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B882" t="s">
         <v>1725</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B883" t="s">
         <v>1727</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B884" t="s">
         <v>1729</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B885" t="s">
         <v>1731</v>
@@ -14346,236 +14349,236 @@
         <v>1732</v>
       </c>
       <c r="B886" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B887" t="s">
         <v>1734</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B888" t="s">
         <v>1736</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B889" t="s">
         <v>1738</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B890" t="s">
         <v>1740</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1741</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B891" t="s">
         <v>1742</v>
-      </c>
-      <c r="B891" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B892" t="s">
         <v>1744</v>
-      </c>
-      <c r="B892" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B893" t="s">
         <v>1746</v>
-      </c>
-      <c r="B893" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B894" t="s">
         <v>1748</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1749</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B895" t="s">
         <v>1750</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B896" t="s">
         <v>1752</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B897" t="s">
         <v>1754</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B898" t="s">
         <v>1756</v>
-      </c>
-      <c r="B898" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B899" t="s">
         <v>1758</v>
-      </c>
-      <c r="B899" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B900" t="s">
         <v>1760</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B901" t="s">
         <v>1762</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B902" t="s">
         <v>1764</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B903" t="s">
         <v>1766</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B904" t="s">
         <v>1768</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1769</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B905" t="s">
         <v>1770</v>
-      </c>
-      <c r="B905" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B906" t="s">
         <v>1772</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B907" t="s">
         <v>1774</v>
-      </c>
-      <c r="B907" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B908" t="s">
         <v>1776</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B909" t="s">
         <v>1778</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B910" t="s">
         <v>1780</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B911" t="s">
         <v>1782</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B912" t="s">
         <v>1784</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B913" t="s">
         <v>1786</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B914" t="s">
         <v>1788</v>
-      </c>
-      <c r="B914" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B915" t="s">
         <v>1790</v>
@@ -14594,127 +14597,127 @@
         <v>1792</v>
       </c>
       <c r="B917" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B918" t="s">
         <v>1794</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B919" t="s">
         <v>1796</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B920" t="s">
         <v>1798</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B921" t="s">
         <v>1800</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B922" t="s">
         <v>1802</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B923" t="s">
         <v>1804</v>
-      </c>
-      <c r="B923" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B924" t="s">
         <v>1806</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B925" t="s">
         <v>1808</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B926" t="s">
         <v>1810</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1811</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B927" t="s">
         <v>1812</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B928" t="s">
         <v>1814</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B929" t="s">
         <v>1816</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B930" t="s">
         <v>1818</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B931" t="s">
         <v>1820</v>
-      </c>
-      <c r="B931" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B932" t="s">
         <v>1822</v>
-      </c>
-      <c r="B932" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="933" spans="1:2">
@@ -14722,260 +14725,260 @@
         <v>1823</v>
       </c>
       <c r="B933" t="s">
-        <v>1824</v>
+        <v>961</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B934" t="s">
         <v>1825</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B935" t="s">
         <v>1827</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B936" t="s">
         <v>1829</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B937" t="s">
         <v>1831</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B938" t="s">
         <v>1833</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B939" t="s">
         <v>1835</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B940" t="s">
         <v>1837</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B941" t="s">
         <v>1839</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B942" t="s">
         <v>1841</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B943" t="s">
         <v>1843</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B944" t="s">
         <v>1845</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B945" t="s">
         <v>1847</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B946" t="s">
         <v>1849</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B947" t="s">
         <v>1851</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B948" t="s">
         <v>1853</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B949" t="s">
         <v>1855</v>
-      </c>
-      <c r="B949" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B950" t="s">
         <v>1857</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B951" t="s">
         <v>1859</v>
-      </c>
-      <c r="B951" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B952" t="s">
         <v>1861</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B953" t="s">
         <v>1863</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B954" t="s">
         <v>1865</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B955" t="s">
         <v>1867</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B956" t="s">
         <v>1869</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1870</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B957" t="s">
         <v>1871</v>
-      </c>
-      <c r="B957" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B958" t="s">
         <v>1873</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B959" t="s">
         <v>1875</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B960" t="s">
         <v>1877</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B961" t="s">
         <v>1879</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B962" t="s">
         <v>1881</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B963" t="s">
         <v>1883</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B964" t="s">
         <v>1885</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B965" t="s">
         <v>1887</v>
@@ -14986,12 +14989,12 @@
         <v>1888</v>
       </c>
       <c r="B966" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B967" t="s">
         <v>1890</v>
@@ -15002,127 +15005,127 @@
         <v>1891</v>
       </c>
       <c r="B968" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B969" t="s">
         <v>1893</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1894</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B970" t="s">
         <v>1895</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1896</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B971" t="s">
         <v>1897</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B972" t="s">
         <v>1899</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B973" t="s">
         <v>1901</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B974" t="s">
         <v>1903</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B975" t="s">
         <v>1905</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B976" t="s">
         <v>1907</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B977" t="s">
         <v>1909</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B978" t="s">
         <v>1911</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B979" t="s">
         <v>1913</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B980" t="s">
         <v>1915</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B981" t="s">
         <v>1917</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B982" t="s">
         <v>1919</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B983" t="s">
         <v>1921</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="984" spans="1:2">
@@ -15130,119 +15133,119 @@
         <v>1922</v>
       </c>
       <c r="B984" t="s">
-        <v>1923</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B985" t="s">
         <v>1924</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B986" t="s">
         <v>1926</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B987" t="s">
         <v>1928</v>
-      </c>
-      <c r="B987" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B988" t="s">
         <v>1930</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B989" t="s">
         <v>1932</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1933</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B990" t="s">
         <v>1934</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B991" t="s">
         <v>1936</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B992" t="s">
         <v>1938</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B993" t="s">
         <v>1940</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B994" t="s">
         <v>1942</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B995" t="s">
         <v>1944</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B996" t="s">
         <v>1946</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B997" t="s">
         <v>1948</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1949</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B998" t="s">
         <v>1950</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1949</v>
       </c>
     </row>
     <row r="999" spans="1:2">
@@ -15250,47 +15253,47 @@
         <v>1951</v>
       </c>
       <c r="B999" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1955</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1956</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1957</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1958</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1959</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1004" t="s">
         <v>1961</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
@@ -15298,100 +15301,100 @@
         <v>1962</v>
       </c>
       <c r="B1005" t="s">
-        <v>1963</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1964</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1967</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1008" t="s">
         <v>1968</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1009" t="s">
         <v>1970</v>
-      </c>
-      <c r="B1009" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1972</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1011" t="s">
         <v>1974</v>
-      </c>
-      <c r="B1011" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1976</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1978</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1979</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1980</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1981</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1982</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1983</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1016" t="s">
         <v>1984</v>
-      </c>
-      <c r="B1016" t="s">
-        <v>1985</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B1017" t="s">
         <v>1986</v>
@@ -15402,76 +15405,76 @@
         <v>1987</v>
       </c>
       <c r="B1018" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1989</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1020" t="s">
         <v>1991</v>
-      </c>
-      <c r="B1020" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1993</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1994</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1995</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1996</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1997</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1998</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1024" t="s">
         <v>1999</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>2000</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B1025" t="s">
         <v>2001</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>2002</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B1026" t="s">
         <v>2003</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>2004</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B1027" t="s">
         <v>2005</v>
@@ -15482,439 +15485,439 @@
         <v>2006</v>
       </c>
       <c r="B1028" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1029" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1030" t="s">
         <v>2010</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1031" t="s">
         <v>2012</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1032" t="s">
         <v>2014</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1033" t="s">
         <v>2016</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1034" t="s">
         <v>2018</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>2019</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1035" t="s">
         <v>2020</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>2021</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1036" t="s">
         <v>2022</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1037" t="s">
         <v>2024</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1038" t="s">
         <v>2026</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>2027</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1039" t="s">
         <v>2028</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1040" t="s">
         <v>2030</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1041" t="s">
         <v>2032</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1042" t="s">
         <v>2034</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1043" t="s">
         <v>2036</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1044" t="s">
         <v>2038</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1045" t="s">
         <v>2040</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1046" t="s">
         <v>2042</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>2043</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1047" t="s">
         <v>2044</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1048" t="s">
         <v>2046</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1049" t="s">
         <v>2048</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1050" t="s">
         <v>2050</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>2051</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1051" t="s">
         <v>2052</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>2053</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1052" t="s">
         <v>2054</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1053" t="s">
         <v>2056</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1054" t="s">
         <v>2058</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1055" t="s">
         <v>2060</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1056" t="s">
         <v>2062</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1057" t="s">
         <v>2064</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1058" t="s">
         <v>2066</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1059" t="s">
         <v>2068</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1060" t="s">
         <v>2070</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1061" t="s">
         <v>2072</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B1062" t="s">
         <v>2074</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>2075</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1063" t="s">
         <v>2076</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>2077</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B1064" t="s">
         <v>2078</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1065" t="s">
         <v>2080</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>2081</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1066" t="s">
         <v>2082</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1067" t="s">
         <v>2084</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>2085</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B1068" t="s">
         <v>2086</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1069" t="s">
         <v>2088</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>2089</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1070" t="s">
         <v>2090</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>2091</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1071" t="s">
         <v>2092</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>2093</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1072" t="s">
         <v>2094</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1073" t="s">
         <v>2096</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>2097</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1074" t="s">
         <v>2098</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>2099</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1075" t="s">
         <v>2100</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>2101</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1076" t="s">
         <v>2102</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>2103</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1077" t="s">
         <v>2104</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>2105</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1078" t="s">
         <v>2106</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>2107</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1079" t="s">
         <v>2108</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>2109</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1080" t="s">
         <v>2110</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1081" t="s">
         <v>2112</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>2113</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1082" t="s">
         <v>2114</v>
-      </c>
-      <c r="B1082" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
@@ -15922,79 +15925,79 @@
         <v>2115</v>
       </c>
       <c r="B1083" t="s">
-        <v>2116</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1084" t="s">
         <v>2117</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1085" t="s">
         <v>2119</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1086" t="s">
         <v>2121</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>2122</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1087" t="s">
         <v>2123</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>2124</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1088" t="s">
         <v>2125</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>2126</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1089" t="s">
         <v>2127</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>2128</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1090" t="s">
         <v>2129</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>2130</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1091" t="s">
         <v>2131</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1092" t="s">
         <v>2133</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
@@ -16002,140 +16005,140 @@
         <v>2134</v>
       </c>
       <c r="B1093" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1094" t="s">
         <v>2136</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1095" t="s">
         <v>2138</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1096" t="s">
         <v>2140</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1097" t="s">
         <v>2142</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>2143</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1098" t="s">
         <v>2144</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1099" t="s">
         <v>2146</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>2147</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1100" t="s">
         <v>2148</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2150</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2151</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1102" t="s">
         <v>2152</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>2153</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2154</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2155</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2156</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2157</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2158</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2159</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1106" t="s">
         <v>2160</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>2161</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2162</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2163</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2164</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2166</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2167</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B1110" t="s">
         <v>2168</v>
@@ -16146,12 +16149,12 @@
         <v>2169</v>
       </c>
       <c r="B1111" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B1112" t="s">
         <v>2171</v>
@@ -16162,199 +16165,199 @@
         <v>2172</v>
       </c>
       <c r="B1113" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1114" t="s">
         <v>2174</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>2175</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1115" t="s">
         <v>2176</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>2177</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B1116" t="s">
         <v>2178</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>2179</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1117" t="s">
         <v>2180</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>2181</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1118" t="s">
         <v>2182</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>2183</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1119" t="s">
         <v>2184</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1120" t="s">
         <v>2186</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>2187</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2188</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2189</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2190</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2191</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2193</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2194</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2195</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2196</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2197</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2198</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2199</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2200</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2201</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2202</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2203</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2204</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2205</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2206</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2208</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2209</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2210</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2212</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2214</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2216</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2217</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1136" t="s">
         <v>2218</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2220</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
@@ -16362,20 +16365,20 @@
         <v>2221</v>
       </c>
       <c r="B1138" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2223</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2224</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B1140" t="s">
         <v>2225</v>
@@ -16386,140 +16389,140 @@
         <v>2226</v>
       </c>
       <c r="B1141" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1142" t="s">
         <v>2228</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1143" t="s">
         <v>2230</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1144" t="s">
         <v>2232</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>2233</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2234</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1146" t="s">
         <v>2236</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>2237</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1147" t="s">
         <v>2238</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2240</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2242</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2244</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2246</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2248</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2250</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2251</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2252</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2253</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2254</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2255</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2256</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2257</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2258</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2259</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B1158" t="s">
         <v>2260</v>
@@ -16538,12 +16541,12 @@
         <v>2262</v>
       </c>
       <c r="B1160" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B1161" t="s">
         <v>2264</v>
@@ -16554,28 +16557,28 @@
         <v>2265</v>
       </c>
       <c r="B1162" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1163" t="s">
         <v>2267</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>2268</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1164" t="s">
         <v>2269</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="B1165" t="s">
         <v>2271</v>
@@ -16586,12 +16589,12 @@
         <v>2272</v>
       </c>
       <c r="B1166" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="B1167" t="s">
         <v>2274</v>
@@ -16602,63 +16605,63 @@
         <v>2275</v>
       </c>
       <c r="B1168" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1169" t="s">
         <v>2277</v>
-      </c>
-      <c r="B1169" t="s">
-        <v>2278</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B1170" t="s">
         <v>2279</v>
-      </c>
-      <c r="B1170" t="s">
-        <v>2280</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1171" t="s">
         <v>2281</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1172" t="s">
         <v>2283</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>2284</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1173" t="s">
         <v>2285</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>2286</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1174" t="s">
         <v>2287</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>2288</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1175" t="s">
         <v>2289</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
@@ -16666,7 +16669,7 @@
         <v>2290</v>
       </c>
       <c r="B1176" t="s">
-        <v>2153</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
@@ -16674,27 +16677,35 @@
         <v>2291</v>
       </c>
       <c r="B1177" t="s">
-        <v>2292</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1178" t="s">
         <v>2293</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>2294</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1179" t="s">
         <v>2295</v>
       </c>
-      <c r="B1179" t="s">
+    </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
         <v>2296</v>
       </c>
+      <c r="B1180" t="s">
+        <v>2297</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2300">
   <si>
     <t>en</t>
   </si>
@@ -965,6 +965,12 @@
   </si>
   <si>
     <t>圣杯</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>混沌立方体</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -7257,7 +7263,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8869,15 +8875,15 @@
         <v>392</v>
       </c>
       <c r="B201" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B202" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -9101,12 +9107,12 @@
         <v>449</v>
       </c>
       <c r="B230" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B231" t="s">
         <v>451</v>
@@ -9301,15 +9307,15 @@
         <v>498</v>
       </c>
       <c r="B255" t="s">
-        <v>203</v>
+        <v>499</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B256" t="s">
-        <v>500</v>
+        <v>203</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9621,15 +9627,15 @@
         <v>577</v>
       </c>
       <c r="B295" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B296" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -9805,12 +9811,12 @@
         <v>622</v>
       </c>
       <c r="B318" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B319" t="s">
         <v>624</v>
@@ -9901,12 +9907,12 @@
         <v>645</v>
       </c>
       <c r="B330" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B331" t="s">
         <v>647</v>
@@ -10981,20 +10987,20 @@
         <v>914</v>
       </c>
       <c r="B465" t="s">
-        <v>621</v>
+        <v>915</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B466" t="s">
-        <v>915</v>
+        <v>623</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B467" t="s">
         <v>917</v>
@@ -11221,15 +11227,15 @@
         <v>972</v>
       </c>
       <c r="B495" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B496" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -11429,15 +11435,15 @@
         <v>1023</v>
       </c>
       <c r="B521" t="s">
-        <v>281</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B522" t="s">
-        <v>1025</v>
+        <v>281</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -11477,15 +11483,15 @@
         <v>1034</v>
       </c>
       <c r="B527" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B528" t="s">
         <v>1035</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -11661,28 +11667,28 @@
         <v>1079</v>
       </c>
       <c r="B550" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B551" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B552" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B553" t="s">
         <v>1083</v>
@@ -11693,12 +11699,12 @@
         <v>1084</v>
       </c>
       <c r="B554" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B555" t="s">
         <v>1086</v>
@@ -12005,12 +12011,12 @@
         <v>1161</v>
       </c>
       <c r="B593" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B594" t="s">
         <v>1163</v>
@@ -12333,12 +12339,12 @@
         <v>1242</v>
       </c>
       <c r="B634" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B635" t="s">
         <v>1244</v>
@@ -13565,12 +13571,12 @@
         <v>1549</v>
       </c>
       <c r="B788" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B789" t="s">
         <v>1551</v>
@@ -13597,15 +13603,15 @@
         <v>1556</v>
       </c>
       <c r="B792" t="s">
-        <v>961</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B793" t="s">
-        <v>1558</v>
+        <v>963</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -13613,20 +13619,20 @@
         <v>1559</v>
       </c>
       <c r="B794" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B795" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B796" t="s">
         <v>1562</v>
@@ -13645,20 +13651,20 @@
         <v>1565</v>
       </c>
       <c r="B798" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B799" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B800" t="s">
         <v>1568</v>
@@ -13957,15 +13963,15 @@
         <v>1641</v>
       </c>
       <c r="B837" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B838" t="s">
         <v>1642</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -14021,23 +14027,23 @@
         <v>1656</v>
       </c>
       <c r="B845" t="s">
-        <v>1608</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B846" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B847" t="s">
-        <v>1659</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -14165,28 +14171,28 @@
         <v>1690</v>
       </c>
       <c r="B863" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B864" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B865" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B866" t="s">
         <v>1694</v>
@@ -14301,12 +14307,12 @@
         <v>1721</v>
       </c>
       <c r="B880" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B881" t="s">
         <v>1723</v>
@@ -14349,12 +14355,12 @@
         <v>1732</v>
       </c>
       <c r="B886" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B887" t="s">
         <v>1734</v>
@@ -14589,20 +14595,20 @@
         <v>1791</v>
       </c>
       <c r="B916" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B917" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B918" t="s">
         <v>1794</v>
@@ -14725,15 +14731,15 @@
         <v>1823</v>
       </c>
       <c r="B933" t="s">
-        <v>961</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B934" t="s">
-        <v>1825</v>
+        <v>963</v>
       </c>
     </row>
     <row r="935" spans="1:2">
@@ -14989,12 +14995,12 @@
         <v>1888</v>
       </c>
       <c r="B966" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B967" t="s">
         <v>1890</v>
@@ -15005,12 +15011,12 @@
         <v>1891</v>
       </c>
       <c r="B968" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B969" t="s">
         <v>1893</v>
@@ -15133,15 +15139,15 @@
         <v>1922</v>
       </c>
       <c r="B984" t="s">
-        <v>1917</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B985" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="986" spans="1:2">
@@ -15253,15 +15259,15 @@
         <v>1951</v>
       </c>
       <c r="B999" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1952</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1953</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
@@ -15301,15 +15307,15 @@
         <v>1962</v>
       </c>
       <c r="B1005" t="s">
-        <v>254</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1006" t="s">
-        <v>1964</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
@@ -15405,12 +15411,12 @@
         <v>1987</v>
       </c>
       <c r="B1018" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1019" t="s">
         <v>1989</v>
@@ -15485,12 +15491,12 @@
         <v>2006</v>
       </c>
       <c r="B1028" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B1029" t="s">
         <v>2008</v>
@@ -15925,15 +15931,15 @@
         <v>2115</v>
       </c>
       <c r="B1083" t="s">
-        <v>524</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B1084" t="s">
-        <v>2117</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
@@ -16005,15 +16011,15 @@
         <v>2134</v>
       </c>
       <c r="B1093" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1094" t="s">
         <v>2135</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>2136</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
@@ -16149,12 +16155,12 @@
         <v>2169</v>
       </c>
       <c r="B1111" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B1112" t="s">
         <v>2171</v>
@@ -16165,12 +16171,12 @@
         <v>2172</v>
       </c>
       <c r="B1113" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="B1114" t="s">
         <v>2174</v>
@@ -16365,15 +16371,15 @@
         <v>2221</v>
       </c>
       <c r="B1138" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2222</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
@@ -16389,12 +16395,12 @@
         <v>2226</v>
       </c>
       <c r="B1141" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="B1142" t="s">
         <v>2228</v>
@@ -16533,20 +16539,20 @@
         <v>2261</v>
       </c>
       <c r="B1159" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="B1160" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B1161" t="s">
         <v>2264</v>
@@ -16557,12 +16563,12 @@
         <v>2265</v>
       </c>
       <c r="B1162" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B1163" t="s">
         <v>2267</v>
@@ -16589,12 +16595,12 @@
         <v>2272</v>
       </c>
       <c r="B1166" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="B1167" t="s">
         <v>2274</v>
@@ -16605,12 +16611,12 @@
         <v>2275</v>
       </c>
       <c r="B1168" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B1169" t="s">
         <v>2277</v>
@@ -16669,23 +16675,23 @@
         <v>2290</v>
       </c>
       <c r="B1176" t="s">
-        <v>68</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="B1177" t="s">
-        <v>2154</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="B1178" t="s">
-        <v>2293</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
@@ -16704,8 +16710,16 @@
         <v>2297</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2299</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2302">
   <si>
     <t>en</t>
   </si>
@@ -5093,6 +5093,12 @@
   </si>
   <si>
     <t>流行史诗队</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>表演者 Popee</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -7263,7 +7269,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14179,28 +14185,28 @@
         <v>1692</v>
       </c>
       <c r="B864" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B865" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B866" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B867" t="s">
         <v>1696</v>
@@ -14315,12 +14321,12 @@
         <v>1723</v>
       </c>
       <c r="B881" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B882" t="s">
         <v>1725</v>
@@ -14363,12 +14369,12 @@
         <v>1734</v>
       </c>
       <c r="B887" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B888" t="s">
         <v>1736</v>
@@ -14603,20 +14609,20 @@
         <v>1793</v>
       </c>
       <c r="B917" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B918" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B919" t="s">
         <v>1796</v>
@@ -14739,15 +14745,15 @@
         <v>1825</v>
       </c>
       <c r="B934" t="s">
-        <v>963</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B935" t="s">
-        <v>1827</v>
+        <v>963</v>
       </c>
     </row>
     <row r="936" spans="1:2">
@@ -15003,12 +15009,12 @@
         <v>1890</v>
       </c>
       <c r="B967" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B968" t="s">
         <v>1892</v>
@@ -15019,12 +15025,12 @@
         <v>1893</v>
       </c>
       <c r="B969" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B970" t="s">
         <v>1895</v>
@@ -15147,15 +15153,15 @@
         <v>1924</v>
       </c>
       <c r="B985" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B986" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="987" spans="1:2">
@@ -15267,15 +15273,15 @@
         <v>1953</v>
       </c>
       <c r="B1000" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1954</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1955</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
@@ -15315,15 +15321,15 @@
         <v>1964</v>
       </c>
       <c r="B1006" t="s">
-        <v>254</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1007" t="s">
-        <v>1966</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
@@ -15419,12 +15425,12 @@
         <v>1989</v>
       </c>
       <c r="B1019" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1020" t="s">
         <v>1991</v>
@@ -15499,12 +15505,12 @@
         <v>2008</v>
       </c>
       <c r="B1029" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B1030" t="s">
         <v>2010</v>
@@ -15939,15 +15945,15 @@
         <v>2117</v>
       </c>
       <c r="B1084" t="s">
-        <v>526</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1085" t="s">
-        <v>2119</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
@@ -16019,15 +16025,15 @@
         <v>2136</v>
       </c>
       <c r="B1094" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1095" t="s">
         <v>2137</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
@@ -16163,12 +16169,12 @@
         <v>2171</v>
       </c>
       <c r="B1112" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B1113" t="s">
         <v>2173</v>
@@ -16179,12 +16185,12 @@
         <v>2174</v>
       </c>
       <c r="B1114" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="B1115" t="s">
         <v>2176</v>
@@ -16379,15 +16385,15 @@
         <v>2223</v>
       </c>
       <c r="B1139" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1140" t="s">
         <v>2224</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
@@ -16403,12 +16409,12 @@
         <v>2228</v>
       </c>
       <c r="B1142" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1143" t="s">
         <v>2230</v>
@@ -16547,20 +16553,20 @@
         <v>2263</v>
       </c>
       <c r="B1160" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="B1161" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="B1162" t="s">
         <v>2266</v>
@@ -16571,12 +16577,12 @@
         <v>2267</v>
       </c>
       <c r="B1163" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="B1164" t="s">
         <v>2269</v>
@@ -16603,12 +16609,12 @@
         <v>2274</v>
       </c>
       <c r="B1167" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="B1168" t="s">
         <v>2276</v>
@@ -16619,12 +16625,12 @@
         <v>2277</v>
       </c>
       <c r="B1169" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="B1170" t="s">
         <v>2279</v>
@@ -16683,23 +16689,23 @@
         <v>2292</v>
       </c>
       <c r="B1177" t="s">
-        <v>68</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="B1178" t="s">
-        <v>2156</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="B1179" t="s">
-        <v>2295</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
@@ -16718,8 +16724,16 @@
         <v>2299</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2301</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1183</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2304">
   <si>
     <t>en</t>
   </si>
@@ -6338,6 +6338,12 @@
   </si>
   <si>
     <t>修补匠的构造</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>小小接管</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -7269,7 +7275,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1183"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15953,15 +15959,15 @@
         <v>2119</v>
       </c>
       <c r="B1085" t="s">
-        <v>526</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B1086" t="s">
-        <v>2121</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
@@ -16033,15 +16039,15 @@
         <v>2138</v>
       </c>
       <c r="B1095" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1096" t="s">
         <v>2139</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>2140</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
@@ -16177,12 +16183,12 @@
         <v>2173</v>
       </c>
       <c r="B1113" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B1114" t="s">
         <v>2175</v>
@@ -16193,12 +16199,12 @@
         <v>2176</v>
       </c>
       <c r="B1115" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B1116" t="s">
         <v>2178</v>
@@ -16393,15 +16399,15 @@
         <v>2225</v>
       </c>
       <c r="B1140" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1141" t="s">
         <v>2226</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>2227</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
@@ -16417,12 +16423,12 @@
         <v>2230</v>
       </c>
       <c r="B1143" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B1144" t="s">
         <v>2232</v>
@@ -16561,20 +16567,20 @@
         <v>2265</v>
       </c>
       <c r="B1161" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B1162" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="B1163" t="s">
         <v>2268</v>
@@ -16585,12 +16591,12 @@
         <v>2269</v>
       </c>
       <c r="B1164" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="B1165" t="s">
         <v>2271</v>
@@ -16617,12 +16623,12 @@
         <v>2276</v>
       </c>
       <c r="B1168" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="B1169" t="s">
         <v>2278</v>
@@ -16633,12 +16639,12 @@
         <v>2279</v>
       </c>
       <c r="B1170" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B1171" t="s">
         <v>2281</v>
@@ -16697,23 +16703,23 @@
         <v>2294</v>
       </c>
       <c r="B1178" t="s">
-        <v>68</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="B1179" t="s">
-        <v>2158</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="B1180" t="s">
-        <v>2297</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
@@ -16732,8 +16738,16 @@
         <v>2301</v>
       </c>
     </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2303</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1183"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2311">
   <si>
     <t>en</t>
   </si>
@@ -3424,6 +3424,9 @@
     <t>超像素</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3448,6 +3451,12 @@
     <t>Hypixel（齿轮）</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>超像素（宝石）</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3466,6 +3475,12 @@
     <t>Hypixel（NPC）</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>超像素（宠物用品）</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3476,6 +3491,12 @@
   </si>
   <si>
     <t>Hypixel（锻造石）</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>超像素（符文）</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -7275,7 +7296,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1183"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11919,116 +11940,116 @@
         <v>1135</v>
       </c>
       <c r="B580" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B581" t="s">
         <v>1137</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B582" t="s">
         <v>1139</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B583" t="s">
         <v>1141</v>
-      </c>
-      <c r="B583" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B584" t="s">
         <v>1143</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B585" t="s">
         <v>1145</v>
-      </c>
-      <c r="B585" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B586" t="s">
         <v>1147</v>
-      </c>
-      <c r="B586" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B587" t="s">
         <v>1149</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B588" t="s">
         <v>1151</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B589" t="s">
         <v>1153</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B590" t="s">
         <v>1155</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B591" t="s">
         <v>1157</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B592" t="s">
         <v>1159</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B593" t="s">
         <v>1161</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B594" t="s">
         <v>1163</v>
@@ -12063,300 +12084,300 @@
         <v>1170</v>
       </c>
       <c r="B598" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B599" t="s">
         <v>1172</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B600" t="s">
         <v>1174</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B601" t="s">
         <v>1176</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B602" t="s">
         <v>1178</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B603" t="s">
         <v>1180</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B604" t="s">
         <v>1182</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B605" t="s">
         <v>1184</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B606" t="s">
         <v>1186</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B607" t="s">
         <v>1188</v>
-      </c>
-      <c r="B607" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B608" t="s">
         <v>1190</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B609" t="s">
         <v>1192</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B610" t="s">
         <v>1194</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B611" t="s">
         <v>1196</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B612" t="s">
         <v>1198</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B613" t="s">
         <v>1200</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B614" t="s">
         <v>1202</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B615" t="s">
         <v>1204</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B616" t="s">
         <v>1206</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B617" t="s">
         <v>1208</v>
-      </c>
-      <c r="B617" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B618" t="s">
         <v>1210</v>
-      </c>
-      <c r="B618" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B619" t="s">
         <v>1212</v>
-      </c>
-      <c r="B619" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B620" t="s">
         <v>1214</v>
-      </c>
-      <c r="B620" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B621" t="s">
         <v>1216</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B622" t="s">
         <v>1218</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B623" t="s">
         <v>1220</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B624" t="s">
         <v>1222</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B625" t="s">
         <v>1224</v>
-      </c>
-      <c r="B625" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B626" t="s">
         <v>1226</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B627" t="s">
         <v>1228</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B628" t="s">
         <v>1230</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B629" t="s">
         <v>1232</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B630" t="s">
         <v>1234</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B631" t="s">
         <v>1236</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B632" t="s">
         <v>1238</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B633" t="s">
         <v>1240</v>
-      </c>
-      <c r="B633" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B634" t="s">
         <v>1242</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B635" t="s">
         <v>1244</v>
@@ -12391,1204 +12412,1204 @@
         <v>1251</v>
       </c>
       <c r="B639" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B640" t="s">
         <v>1253</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B641" t="s">
         <v>1255</v>
-      </c>
-      <c r="B641" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B642" t="s">
         <v>1257</v>
-      </c>
-      <c r="B642" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B643" t="s">
         <v>1259</v>
-      </c>
-      <c r="B643" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B644" t="s">
         <v>1261</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B645" t="s">
         <v>1263</v>
-      </c>
-      <c r="B645" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B646" t="s">
         <v>1265</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B647" t="s">
         <v>1267</v>
-      </c>
-      <c r="B647" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B648" t="s">
         <v>1269</v>
-      </c>
-      <c r="B648" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B649" t="s">
         <v>1271</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B650" t="s">
         <v>1273</v>
-      </c>
-      <c r="B650" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B651" t="s">
         <v>1275</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B652" t="s">
         <v>1277</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B653" t="s">
         <v>1279</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B654" t="s">
         <v>1281</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B655" t="s">
         <v>1283</v>
-      </c>
-      <c r="B655" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B656" t="s">
         <v>1285</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B657" t="s">
         <v>1287</v>
-      </c>
-      <c r="B657" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B658" t="s">
         <v>1289</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B659" t="s">
         <v>1291</v>
-      </c>
-      <c r="B659" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B660" t="s">
         <v>1293</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B661" t="s">
         <v>1295</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B662" t="s">
         <v>1297</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B663" t="s">
         <v>1299</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B664" t="s">
         <v>1301</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B665" t="s">
         <v>1303</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B666" t="s">
         <v>1305</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B667" t="s">
         <v>1307</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B668" t="s">
         <v>1309</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B669" t="s">
         <v>1311</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B670" t="s">
         <v>1313</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B671" t="s">
         <v>1315</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B672" t="s">
         <v>1317</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B673" t="s">
         <v>1319</v>
-      </c>
-      <c r="B673" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B674" t="s">
         <v>1321</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B675" t="s">
         <v>1323</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B676" t="s">
         <v>1325</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B677" t="s">
         <v>1327</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B678" t="s">
         <v>1329</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B679" t="s">
         <v>1331</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B680" t="s">
         <v>1333</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B681" t="s">
         <v>1335</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B682" t="s">
         <v>1337</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B683" t="s">
         <v>1339</v>
-      </c>
-      <c r="B683" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B684" t="s">
         <v>1341</v>
-      </c>
-      <c r="B684" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B685" t="s">
         <v>1343</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B686" t="s">
         <v>1345</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B687" t="s">
         <v>1347</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B688" t="s">
         <v>1349</v>
-      </c>
-      <c r="B688" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B689" t="s">
         <v>1351</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B690" t="s">
         <v>1353</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B691" t="s">
         <v>1355</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B692" t="s">
         <v>1357</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B693" t="s">
         <v>1359</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B694" t="s">
         <v>1361</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B695" t="s">
         <v>1363</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B696" t="s">
         <v>1365</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B697" t="s">
         <v>1367</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B698" t="s">
         <v>1369</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B699" t="s">
         <v>1371</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B700" t="s">
         <v>1373</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B701" t="s">
         <v>1375</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B702" t="s">
         <v>1377</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B703" t="s">
         <v>1379</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B704" t="s">
         <v>1381</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B705" t="s">
         <v>1383</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B706" t="s">
         <v>1385</v>
-      </c>
-      <c r="B706" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B707" t="s">
         <v>1387</v>
-      </c>
-      <c r="B707" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B708" t="s">
         <v>1389</v>
-      </c>
-      <c r="B708" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B709" t="s">
         <v>1391</v>
-      </c>
-      <c r="B709" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B710" t="s">
         <v>1393</v>
-      </c>
-      <c r="B710" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B711" t="s">
         <v>1395</v>
-      </c>
-      <c r="B711" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B712" t="s">
         <v>1397</v>
-      </c>
-      <c r="B712" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B713" t="s">
         <v>1399</v>
-      </c>
-      <c r="B713" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B714" t="s">
         <v>1401</v>
-      </c>
-      <c r="B714" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B715" t="s">
         <v>1403</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B716" t="s">
         <v>1405</v>
-      </c>
-      <c r="B716" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B717" t="s">
         <v>1407</v>
-      </c>
-      <c r="B717" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B718" t="s">
         <v>1409</v>
-      </c>
-      <c r="B718" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B719" t="s">
         <v>1411</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B720" t="s">
         <v>1413</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B721" t="s">
         <v>1415</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B722" t="s">
         <v>1417</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B723" t="s">
         <v>1419</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B724" t="s">
         <v>1421</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B725" t="s">
         <v>1423</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B726" t="s">
         <v>1425</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B727" t="s">
         <v>1427</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B728" t="s">
         <v>1429</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B729" t="s">
         <v>1431</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B730" t="s">
         <v>1433</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B731" t="s">
         <v>1435</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B732" t="s">
         <v>1437</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B733" t="s">
         <v>1439</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B734" t="s">
         <v>1441</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B735" t="s">
         <v>1443</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B736" t="s">
         <v>1445</v>
-      </c>
-      <c r="B736" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B737" t="s">
         <v>1447</v>
-      </c>
-      <c r="B737" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B738" t="s">
         <v>1449</v>
-      </c>
-      <c r="B738" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B739" t="s">
         <v>1451</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B740" t="s">
         <v>1453</v>
-      </c>
-      <c r="B740" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B741" t="s">
         <v>1455</v>
-      </c>
-      <c r="B741" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B742" t="s">
         <v>1457</v>
-      </c>
-      <c r="B742" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B743" t="s">
         <v>1459</v>
-      </c>
-      <c r="B743" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B744" t="s">
         <v>1461</v>
-      </c>
-      <c r="B744" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B745" t="s">
         <v>1463</v>
-      </c>
-      <c r="B745" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B746" t="s">
         <v>1465</v>
-      </c>
-      <c r="B746" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B747" t="s">
         <v>1467</v>
-      </c>
-      <c r="B747" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B748" t="s">
         <v>1469</v>
-      </c>
-      <c r="B748" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B749" t="s">
         <v>1471</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B750" t="s">
         <v>1473</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B751" t="s">
         <v>1475</v>
-      </c>
-      <c r="B751" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B752" t="s">
         <v>1477</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B753" t="s">
         <v>1479</v>
-      </c>
-      <c r="B753" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B754" t="s">
         <v>1481</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B755" t="s">
         <v>1483</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B756" t="s">
         <v>1485</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B757" t="s">
         <v>1487</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B758" t="s">
         <v>1489</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B759" t="s">
         <v>1491</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B760" t="s">
         <v>1493</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B761" t="s">
         <v>1495</v>
-      </c>
-      <c r="B761" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B762" t="s">
         <v>1497</v>
-      </c>
-      <c r="B762" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B763" t="s">
         <v>1499</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B764" t="s">
         <v>1501</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B765" t="s">
         <v>1503</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B766" t="s">
         <v>1505</v>
-      </c>
-      <c r="B766" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B767" t="s">
         <v>1507</v>
-      </c>
-      <c r="B767" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B768" t="s">
         <v>1509</v>
-      </c>
-      <c r="B768" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B769" t="s">
         <v>1511</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B770" t="s">
         <v>1513</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B771" t="s">
         <v>1515</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B772" t="s">
         <v>1517</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B773" t="s">
         <v>1519</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B774" t="s">
         <v>1521</v>
-      </c>
-      <c r="B774" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B775" t="s">
         <v>1523</v>
-      </c>
-      <c r="B775" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B776" t="s">
         <v>1525</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B777" t="s">
         <v>1527</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B778" t="s">
         <v>1529</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B779" t="s">
         <v>1531</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B780" t="s">
         <v>1533</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1534</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B781" t="s">
         <v>1535</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B782" t="s">
         <v>1537</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B783" t="s">
         <v>1539</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B784" t="s">
         <v>1541</v>
-      </c>
-      <c r="B784" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B785" t="s">
         <v>1543</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B786" t="s">
         <v>1545</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B787" t="s">
         <v>1547</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B788" t="s">
         <v>1549</v>
-      </c>
-      <c r="B788" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B789" t="s">
         <v>1551</v>
@@ -13623,7 +13644,7 @@
         <v>1558</v>
       </c>
       <c r="B793" t="s">
-        <v>963</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="794" spans="1:2">
@@ -13639,68 +13660,68 @@
         <v>1561</v>
       </c>
       <c r="B795" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B796" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B797" t="s">
-        <v>1564</v>
+        <v>963</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B798" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B799" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B800" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B801" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B802" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B803" t="s">
         <v>1574</v>
@@ -13711,279 +13732,279 @@
         <v>1575</v>
       </c>
       <c r="B804" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B805" t="s">
         <v>1577</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B806" t="s">
         <v>1579</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B807" t="s">
         <v>1581</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B808" t="s">
         <v>1583</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B809" t="s">
         <v>1585</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B810" t="s">
         <v>1587</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B811" t="s">
         <v>1589</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B812" t="s">
         <v>1591</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B813" t="s">
         <v>1593</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B814" t="s">
         <v>1595</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B815" t="s">
         <v>1597</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B816" t="s">
         <v>1599</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B817" t="s">
         <v>1601</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B818" t="s">
         <v>1603</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B819" t="s">
         <v>1605</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B820" t="s">
         <v>1607</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B821" t="s">
         <v>1609</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B822" t="s">
         <v>1611</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B823" t="s">
         <v>1613</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B824" t="s">
         <v>1615</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B825" t="s">
         <v>1617</v>
-      </c>
-      <c r="B825" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B826" t="s">
         <v>1619</v>
-      </c>
-      <c r="B826" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B827" t="s">
         <v>1621</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B828" t="s">
         <v>1623</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B829" t="s">
         <v>1625</v>
-      </c>
-      <c r="B829" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B830" t="s">
         <v>1627</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B831" t="s">
         <v>1629</v>
-      </c>
-      <c r="B831" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B832" t="s">
         <v>1631</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B833" t="s">
         <v>1633</v>
-      </c>
-      <c r="B833" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B834" t="s">
         <v>1635</v>
-      </c>
-      <c r="B834" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B835" t="s">
         <v>1637</v>
-      </c>
-      <c r="B835" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B836" t="s">
         <v>1639</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B837" t="s">
         <v>1641</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B838" t="s">
         <v>1643</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="839" spans="1:2">
@@ -14015,39 +14036,39 @@
         <v>1650</v>
       </c>
       <c r="B842" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B843" t="s">
         <v>1652</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B844" t="s">
         <v>1654</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B845" t="s">
         <v>1656</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B846" t="s">
         <v>1658</v>
-      </c>
-      <c r="B846" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -14055,31 +14076,31 @@
         <v>1659</v>
       </c>
       <c r="B847" t="s">
-        <v>1610</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B848" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B849" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B850" t="s">
-        <v>1665</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="851" spans="1:2">
@@ -14087,116 +14108,116 @@
         <v>1666</v>
       </c>
       <c r="B851" t="s">
-        <v>1667</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B852" t="s">
         <v>1668</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B853" t="s">
         <v>1670</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B854" t="s">
         <v>1672</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1673</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B855" t="s">
         <v>1674</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1675</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B856" t="s">
         <v>1676</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B857" t="s">
         <v>1678</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B858" t="s">
         <v>1680</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B859" t="s">
         <v>1682</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B860" t="s">
         <v>1684</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1685</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B861" t="s">
         <v>1686</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1687</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B862" t="s">
         <v>1688</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B863" t="s">
         <v>1690</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1691</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B864" t="s">
         <v>1692</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B865" t="s">
         <v>1694</v>
@@ -14207,36 +14228,36 @@
         <v>1695</v>
       </c>
       <c r="B866" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B867" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B868" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B869" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B870" t="s">
         <v>1702</v>
@@ -14247,92 +14268,92 @@
         <v>1703</v>
       </c>
       <c r="B871" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B872" t="s">
         <v>1705</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B873" t="s">
         <v>1707</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B874" t="s">
         <v>1709</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B875" t="s">
         <v>1711</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B876" t="s">
         <v>1713</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B877" t="s">
         <v>1715</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B878" t="s">
         <v>1717</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B879" t="s">
         <v>1719</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B880" t="s">
         <v>1721</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B881" t="s">
         <v>1723</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B882" t="s">
         <v>1725</v>
@@ -14367,20 +14388,20 @@
         <v>1732</v>
       </c>
       <c r="B886" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B887" t="s">
         <v>1734</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B888" t="s">
         <v>1736</v>
@@ -14415,212 +14436,212 @@
         <v>1743</v>
       </c>
       <c r="B892" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B893" t="s">
         <v>1745</v>
-      </c>
-      <c r="B893" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B894" t="s">
         <v>1747</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B895" t="s">
         <v>1749</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B896" t="s">
         <v>1751</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B897" t="s">
         <v>1753</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B898" t="s">
         <v>1755</v>
-      </c>
-      <c r="B898" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B899" t="s">
         <v>1757</v>
-      </c>
-      <c r="B899" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B900" t="s">
         <v>1759</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B901" t="s">
         <v>1761</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B902" t="s">
         <v>1763</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B903" t="s">
         <v>1765</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B904" t="s">
         <v>1767</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B905" t="s">
         <v>1769</v>
-      </c>
-      <c r="B905" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B906" t="s">
         <v>1771</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B907" t="s">
         <v>1773</v>
-      </c>
-      <c r="B907" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B908" t="s">
         <v>1775</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B909" t="s">
         <v>1777</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B910" t="s">
         <v>1779</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B911" t="s">
         <v>1781</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B912" t="s">
         <v>1783</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1784</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B913" t="s">
         <v>1785</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B914" t="s">
         <v>1787</v>
-      </c>
-      <c r="B914" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B915" t="s">
         <v>1789</v>
-      </c>
-      <c r="B915" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B916" t="s">
         <v>1791</v>
-      </c>
-      <c r="B916" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B917" t="s">
         <v>1793</v>
-      </c>
-      <c r="B917" t="s">
-        <v>1794</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B918" t="s">
         <v>1795</v>
@@ -14631,28 +14652,28 @@
         <v>1796</v>
       </c>
       <c r="B919" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B920" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B921" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B922" t="s">
         <v>1802</v>
@@ -14663,103 +14684,103 @@
         <v>1803</v>
       </c>
       <c r="B923" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B924" t="s">
         <v>1805</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B925" t="s">
         <v>1807</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B926" t="s">
         <v>1809</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1810</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B927" t="s">
         <v>1811</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B928" t="s">
         <v>1813</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B929" t="s">
         <v>1815</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B930" t="s">
         <v>1817</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B931" t="s">
         <v>1819</v>
-      </c>
-      <c r="B931" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B932" t="s">
         <v>1821</v>
-      </c>
-      <c r="B932" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B933" t="s">
         <v>1823</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B934" t="s">
         <v>1825</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B935" t="s">
         <v>1827</v>
-      </c>
-      <c r="B935" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="936" spans="1:2">
@@ -14791,236 +14812,236 @@
         <v>1834</v>
       </c>
       <c r="B939" t="s">
-        <v>1835</v>
+        <v>963</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B940" t="s">
         <v>1836</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B941" t="s">
         <v>1838</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B942" t="s">
         <v>1840</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B943" t="s">
         <v>1842</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B944" t="s">
         <v>1844</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B945" t="s">
         <v>1846</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B946" t="s">
         <v>1848</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1849</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B947" t="s">
         <v>1850</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B948" t="s">
         <v>1852</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B949" t="s">
         <v>1854</v>
-      </c>
-      <c r="B949" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B950" t="s">
         <v>1856</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B951" t="s">
         <v>1858</v>
-      </c>
-      <c r="B951" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B952" t="s">
         <v>1860</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B953" t="s">
         <v>1862</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B954" t="s">
         <v>1864</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B955" t="s">
         <v>1866</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B956" t="s">
         <v>1868</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B957" t="s">
         <v>1870</v>
-      </c>
-      <c r="B957" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B958" t="s">
         <v>1872</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B959" t="s">
         <v>1874</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B960" t="s">
         <v>1876</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B961" t="s">
         <v>1878</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B962" t="s">
         <v>1880</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B963" t="s">
         <v>1882</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B964" t="s">
         <v>1884</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B965" t="s">
         <v>1886</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B966" t="s">
         <v>1888</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B967" t="s">
         <v>1890</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B968" t="s">
         <v>1892</v>
@@ -15039,20 +15060,20 @@
         <v>1895</v>
       </c>
       <c r="B970" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B971" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B972" t="s">
         <v>1899</v>
@@ -15071,103 +15092,103 @@
         <v>1902</v>
       </c>
       <c r="B974" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B975" t="s">
         <v>1904</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1905</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B976" t="s">
         <v>1906</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1907</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B977" t="s">
         <v>1908</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1909</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B978" t="s">
         <v>1910</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B979" t="s">
         <v>1912</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B980" t="s">
         <v>1914</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1915</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B981" t="s">
         <v>1916</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1917</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B982" t="s">
         <v>1918</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B983" t="s">
         <v>1920</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1921</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B984" t="s">
         <v>1922</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B985" t="s">
         <v>1924</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B986" t="s">
         <v>1926</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1921</v>
       </c>
     </row>
     <row r="987" spans="1:2">
@@ -15199,95 +15220,95 @@
         <v>1933</v>
       </c>
       <c r="B990" t="s">
-        <v>1934</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B991" t="s">
         <v>1935</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B992" t="s">
         <v>1937</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B993" t="s">
         <v>1939</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B994" t="s">
         <v>1941</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B995" t="s">
         <v>1943</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B996" t="s">
         <v>1945</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B997" t="s">
         <v>1947</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B998" t="s">
         <v>1949</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B999" t="s">
         <v>1951</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1955</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
@@ -15319,23 +15340,23 @@
         <v>1962</v>
       </c>
       <c r="B1005" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1964</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
@@ -15367,76 +15388,76 @@
         <v>1973</v>
       </c>
       <c r="B1011" t="s">
-        <v>1974</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1975</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1977</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1979</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1981</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1982</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1016" t="s">
         <v>1983</v>
-      </c>
-      <c r="B1016" t="s">
-        <v>1984</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1017" t="s">
         <v>1985</v>
-      </c>
-      <c r="B1017" t="s">
-        <v>1986</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1018" t="s">
         <v>1987</v>
-      </c>
-      <c r="B1018" t="s">
-        <v>1988</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1989</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B1020" t="s">
         <v>1991</v>
@@ -15471,52 +15492,52 @@
         <v>1998</v>
       </c>
       <c r="B1024" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1025" t="s">
         <v>2000</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1026" t="s">
         <v>2002</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1027" t="s">
         <v>2004</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1028" t="s">
         <v>2006</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1029" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B1030" t="s">
         <v>2010</v>
@@ -15551,423 +15572,423 @@
         <v>2017</v>
       </c>
       <c r="B1034" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B1035" t="s">
         <v>2019</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>2020</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1036" t="s">
         <v>2021</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>2022</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B1037" t="s">
         <v>2023</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>2024</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1038" t="s">
         <v>2025</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B1039" t="s">
         <v>2027</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>2028</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1040" t="s">
         <v>2029</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>2030</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B1041" t="s">
         <v>2031</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>2032</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B1042" t="s">
         <v>2033</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>2034</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B1043" t="s">
         <v>2035</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>2036</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B1044" t="s">
         <v>2037</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>2038</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1045" t="s">
         <v>2039</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>2040</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B1046" t="s">
         <v>2041</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>2042</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1047" t="s">
         <v>2043</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>2044</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B1048" t="s">
         <v>2045</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B1049" t="s">
         <v>2047</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>2048</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1050" t="s">
         <v>2049</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B1051" t="s">
         <v>2051</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B1052" t="s">
         <v>2053</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>2054</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B1053" t="s">
         <v>2055</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>2056</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1054" t="s">
         <v>2057</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>2058</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1055" t="s">
         <v>2059</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>2060</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1056" t="s">
         <v>2061</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>2062</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1057" t="s">
         <v>2063</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>2064</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1058" t="s">
         <v>2065</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>2066</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1059" t="s">
         <v>2067</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1060" t="s">
         <v>2069</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1061" t="s">
         <v>2071</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>2072</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1062" t="s">
         <v>2073</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1063" t="s">
         <v>2075</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1064" t="s">
         <v>2077</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>2078</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1065" t="s">
         <v>2079</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1066" t="s">
         <v>2081</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>2082</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1067" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>2084</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1068" t="s">
         <v>2085</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1069" t="s">
         <v>2087</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>2088</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1070" t="s">
         <v>2089</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1071" t="s">
         <v>2091</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>2092</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1072" t="s">
         <v>2093</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1073" t="s">
         <v>2095</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1074" t="s">
         <v>2097</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1075" t="s">
         <v>2099</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1076" t="s">
         <v>2101</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1077" t="s">
         <v>2103</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1078" t="s">
         <v>2105</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1079" t="s">
         <v>2107</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1080" t="s">
         <v>2109</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1081" t="s">
         <v>2111</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>2112</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1082" t="s">
         <v>2113</v>
-      </c>
-      <c r="B1082" t="s">
-        <v>2114</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1083" t="s">
         <v>2115</v>
-      </c>
-      <c r="B1083" t="s">
-        <v>2116</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1084" t="s">
         <v>2117</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1085" t="s">
         <v>2119</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1086" t="s">
         <v>2121</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
@@ -15999,55 +16020,55 @@
         <v>2128</v>
       </c>
       <c r="B1090" t="s">
-        <v>2129</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1091" t="s">
         <v>2130</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>2131</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1092" t="s">
         <v>2132</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>2133</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1093" t="s">
         <v>2134</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1094" t="s">
         <v>2136</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1095" t="s">
         <v>2138</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1096" t="s">
         <v>2140</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
@@ -16079,116 +16100,116 @@
         <v>2147</v>
       </c>
       <c r="B1100" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2149</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1102" t="s">
         <v>2151</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>2152</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2153</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2155</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2157</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2158</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1106" t="s">
         <v>2159</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2161</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2163</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2165</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2166</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1110" t="s">
         <v>2167</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>2168</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1111" t="s">
         <v>2169</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1112" t="s">
         <v>2171</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1113" t="s">
         <v>2173</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B1114" t="s">
         <v>2175</v>
@@ -16207,20 +16228,20 @@
         <v>2178</v>
       </c>
       <c r="B1116" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B1117" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="B1118" t="s">
         <v>2182</v>
@@ -16239,175 +16260,175 @@
         <v>2185</v>
       </c>
       <c r="B1120" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2187</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2188</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2189</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2191</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2193</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2194</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2195</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2196</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2197</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2199</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2200</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2201</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2203</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2205</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2206</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2207</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2208</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2209</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2210</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2211</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2212</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2213</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2214</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2215</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2216</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B1136" t="s">
         <v>2217</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>2218</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2219</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2220</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2221</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2222</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2223</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2224</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1140" t="s">
         <v>2225</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>2226</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1141" t="s">
         <v>2227</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>2226</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
@@ -16431,15 +16452,15 @@
         <v>2232</v>
       </c>
       <c r="B1144" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2233</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2234</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
@@ -16463,116 +16484,116 @@
         <v>2239</v>
       </c>
       <c r="B1148" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2241</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2242</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2243</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2244</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2245</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2246</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2247</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2248</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2249</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2250</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2251</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2253</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2254</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2255</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2256</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2257</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B1158" t="s">
         <v>2259</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>2260</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1159" t="s">
         <v>2261</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2263</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1161" t="s">
         <v>2265</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>2266</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B1162" t="s">
         <v>2267</v>
@@ -16583,36 +16604,36 @@
         <v>2268</v>
       </c>
       <c r="B1163" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="B1164" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="B1165" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="B1166" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="B1167" t="s">
         <v>2275</v>
@@ -16647,20 +16668,20 @@
         <v>2281</v>
       </c>
       <c r="B1171" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B1172" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B1173" t="s">
         <v>2285</v>
@@ -16679,39 +16700,39 @@
         <v>2288</v>
       </c>
       <c r="B1175" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B1176" t="s">
         <v>2290</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>2291</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2292</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1178" t="s">
         <v>2294</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>2295</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B1179" t="s">
         <v>2296</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
@@ -16719,35 +16740,67 @@
         <v>2297</v>
       </c>
       <c r="B1180" t="s">
-        <v>2160</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="B1181" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="B1182" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="B1183" t="s">
-        <v>2303</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1183"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2313">
   <si>
     <t>en</t>
   </si>
@@ -5189,6 +5189,12 @@
   </si>
   <si>
     <t>雷顿教授</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Zomboid 项目</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -7296,7 +7302,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14388,12 +14394,12 @@
         <v>1732</v>
       </c>
       <c r="B886" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B887" t="s">
         <v>1734</v>
@@ -14436,12 +14442,12 @@
         <v>1743</v>
       </c>
       <c r="B892" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B893" t="s">
         <v>1745</v>
@@ -14676,20 +14682,20 @@
         <v>1802</v>
       </c>
       <c r="B922" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B923" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B924" t="s">
         <v>1805</v>
@@ -14812,15 +14818,15 @@
         <v>1834</v>
       </c>
       <c r="B939" t="s">
-        <v>963</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B940" t="s">
-        <v>1836</v>
+        <v>963</v>
       </c>
     </row>
     <row r="941" spans="1:2">
@@ -15076,12 +15082,12 @@
         <v>1899</v>
       </c>
       <c r="B972" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B973" t="s">
         <v>1901</v>
@@ -15092,12 +15098,12 @@
         <v>1902</v>
       </c>
       <c r="B974" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B975" t="s">
         <v>1904</v>
@@ -15220,15 +15226,15 @@
         <v>1933</v>
       </c>
       <c r="B990" t="s">
-        <v>1928</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B991" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="992" spans="1:2">
@@ -15340,15 +15346,15 @@
         <v>1962</v>
       </c>
       <c r="B1005" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1963</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1964</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
@@ -15388,15 +15394,15 @@
         <v>1973</v>
       </c>
       <c r="B1011" t="s">
-        <v>254</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1012" t="s">
-        <v>1975</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
@@ -15492,12 +15498,12 @@
         <v>1998</v>
       </c>
       <c r="B1024" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1025" t="s">
         <v>2000</v>
@@ -15572,12 +15578,12 @@
         <v>2017</v>
       </c>
       <c r="B1034" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B1035" t="s">
         <v>2019</v>
@@ -16020,15 +16026,15 @@
         <v>2128</v>
       </c>
       <c r="B1090" t="s">
-        <v>526</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B1091" t="s">
-        <v>2130</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
@@ -16100,15 +16106,15 @@
         <v>2147</v>
       </c>
       <c r="B1100" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2148</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
@@ -16244,12 +16250,12 @@
         <v>2182</v>
       </c>
       <c r="B1118" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B1119" t="s">
         <v>2184</v>
@@ -16260,12 +16266,12 @@
         <v>2185</v>
       </c>
       <c r="B1120" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B1121" t="s">
         <v>2187</v>
@@ -16460,15 +16466,15 @@
         <v>2234</v>
       </c>
       <c r="B1145" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B1146" t="s">
         <v>2235</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>2236</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
@@ -16484,12 +16490,12 @@
         <v>2239</v>
       </c>
       <c r="B1148" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B1149" t="s">
         <v>2241</v>
@@ -16628,20 +16634,20 @@
         <v>2274</v>
       </c>
       <c r="B1166" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="B1167" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B1168" t="s">
         <v>2277</v>
@@ -16652,12 +16658,12 @@
         <v>2278</v>
       </c>
       <c r="B1169" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="B1170" t="s">
         <v>2280</v>
@@ -16684,12 +16690,12 @@
         <v>2285</v>
       </c>
       <c r="B1173" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="B1174" t="s">
         <v>2287</v>
@@ -16700,12 +16706,12 @@
         <v>2288</v>
       </c>
       <c r="B1175" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B1176" t="s">
         <v>2290</v>
@@ -16764,23 +16770,23 @@
         <v>2303</v>
       </c>
       <c r="B1183" t="s">
-        <v>68</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="B1184" t="s">
-        <v>2167</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="B1185" t="s">
-        <v>2306</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -16799,8 +16805,16 @@
         <v>2310</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>2312</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2316">
   <si>
     <t>en</t>
   </si>
@@ -5573,6 +5573,12 @@
   </si>
   <si>
     <t>魔多之影</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>鲨鱼</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -7305,7 +7311,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15101,12 +15107,12 @@
         <v>1902</v>
       </c>
       <c r="B974" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B975" t="s">
         <v>1904</v>
@@ -15117,12 +15123,12 @@
         <v>1905</v>
       </c>
       <c r="B976" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B977" t="s">
         <v>1907</v>
@@ -15245,15 +15251,15 @@
         <v>1936</v>
       </c>
       <c r="B992" t="s">
-        <v>1931</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B993" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="994" spans="1:2">
@@ -15365,15 +15371,15 @@
         <v>1965</v>
       </c>
       <c r="B1007" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1008" t="s">
         <v>1966</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>1967</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
@@ -15413,15 +15419,15 @@
         <v>1976</v>
       </c>
       <c r="B1013" t="s">
-        <v>255</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1014" t="s">
-        <v>1978</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
@@ -15517,12 +15523,12 @@
         <v>2001</v>
       </c>
       <c r="B1026" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B1027" t="s">
         <v>2003</v>
@@ -15597,12 +15603,12 @@
         <v>2020</v>
       </c>
       <c r="B1036" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B1037" t="s">
         <v>2022</v>
@@ -16045,15 +16051,15 @@
         <v>2131</v>
       </c>
       <c r="B1092" t="s">
-        <v>527</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B1093" t="s">
-        <v>2133</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
@@ -16125,15 +16131,15 @@
         <v>2150</v>
       </c>
       <c r="B1102" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2151</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2152</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
@@ -16269,12 +16275,12 @@
         <v>2185</v>
       </c>
       <c r="B1120" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B1121" t="s">
         <v>2187</v>
@@ -16285,12 +16291,12 @@
         <v>2188</v>
       </c>
       <c r="B1122" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B1123" t="s">
         <v>2190</v>
@@ -16485,15 +16491,15 @@
         <v>2237</v>
       </c>
       <c r="B1147" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2238</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
@@ -16509,12 +16515,12 @@
         <v>2242</v>
       </c>
       <c r="B1150" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B1151" t="s">
         <v>2244</v>
@@ -16653,20 +16659,20 @@
         <v>2277</v>
       </c>
       <c r="B1168" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="B1169" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="B1170" t="s">
         <v>2280</v>
@@ -16677,12 +16683,12 @@
         <v>2281</v>
       </c>
       <c r="B1171" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B1172" t="s">
         <v>2283</v>
@@ -16709,12 +16715,12 @@
         <v>2288</v>
       </c>
       <c r="B1175" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B1176" t="s">
         <v>2290</v>
@@ -16725,12 +16731,12 @@
         <v>2291</v>
       </c>
       <c r="B1177" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="B1178" t="s">
         <v>2293</v>
@@ -16789,23 +16795,23 @@
         <v>2306</v>
       </c>
       <c r="B1185" t="s">
-        <v>68</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="B1186" t="s">
-        <v>2170</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="B1187" t="s">
-        <v>2309</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
@@ -16824,8 +16830,16 @@
         <v>2313</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2315</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -1921,6 +1921,12 @@
     <t>童话故事</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>坠落</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -6953,12 +6959,6 @@
   </si>
   <si>
     <t>超像素（变异）标签</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>坠落</t>
   </si>
   <si>
     <t>Summer Drop 2025</t>
@@ -9971,12 +9971,12 @@
         <v>648</v>
       </c>
       <c r="B332" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B333" t="s">
         <v>650</v>
@@ -11051,20 +11051,20 @@
         <v>917</v>
       </c>
       <c r="B467" t="s">
-        <v>624</v>
+        <v>918</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B468" t="s">
-        <v>918</v>
+        <v>624</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B469" t="s">
         <v>920</v>
@@ -11291,15 +11291,15 @@
         <v>975</v>
       </c>
       <c r="B497" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B498" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -11499,15 +11499,15 @@
         <v>1026</v>
       </c>
       <c r="B523" t="s">
-        <v>282</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B524" t="s">
-        <v>1028</v>
+        <v>282</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -11547,15 +11547,15 @@
         <v>1037</v>
       </c>
       <c r="B529" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B530" t="s">
         <v>1038</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -11731,28 +11731,28 @@
         <v>1082</v>
       </c>
       <c r="B552" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B553" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B554" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B555" t="s">
         <v>1086</v>
@@ -11763,12 +11763,12 @@
         <v>1087</v>
       </c>
       <c r="B556" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B557" t="s">
         <v>1089</v>
@@ -11963,12 +11963,12 @@
         <v>1136</v>
       </c>
       <c r="B581" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B582" t="s">
         <v>1138</v>
@@ -12107,12 +12107,12 @@
         <v>1171</v>
       </c>
       <c r="B599" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B600" t="s">
         <v>1173</v>
@@ -12435,12 +12435,12 @@
         <v>1252</v>
       </c>
       <c r="B640" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B641" t="s">
         <v>1254</v>
@@ -13667,12 +13667,12 @@
         <v>1559</v>
       </c>
       <c r="B794" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B795" t="s">
         <v>1561</v>
@@ -13699,15 +13699,15 @@
         <v>1566</v>
       </c>
       <c r="B798" t="s">
-        <v>964</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B799" t="s">
-        <v>1568</v>
+        <v>966</v>
       </c>
     </row>
     <row r="800" spans="1:2">
@@ -13715,20 +13715,20 @@
         <v>1569</v>
       </c>
       <c r="B800" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B801" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B802" t="s">
         <v>1572</v>
@@ -13747,20 +13747,20 @@
         <v>1575</v>
       </c>
       <c r="B804" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B805" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B806" t="s">
         <v>1578</v>
@@ -14059,15 +14059,15 @@
         <v>1651</v>
       </c>
       <c r="B843" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B844" t="s">
         <v>1652</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="845" spans="1:2">
@@ -14123,23 +14123,23 @@
         <v>1666</v>
       </c>
       <c r="B851" t="s">
-        <v>1618</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B852" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B853" t="s">
-        <v>1669</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="854" spans="1:2">
@@ -14275,28 +14275,28 @@
         <v>1702</v>
       </c>
       <c r="B870" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B871" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B872" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B873" t="s">
         <v>1706</v>
@@ -14419,12 +14419,12 @@
         <v>1735</v>
       </c>
       <c r="B888" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B889" t="s">
         <v>1737</v>
@@ -14467,12 +14467,12 @@
         <v>1746</v>
       </c>
       <c r="B894" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B895" t="s">
         <v>1748</v>
@@ -14707,20 +14707,20 @@
         <v>1805</v>
       </c>
       <c r="B924" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B925" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B926" t="s">
         <v>1808</v>
@@ -14843,15 +14843,15 @@
         <v>1837</v>
       </c>
       <c r="B941" t="s">
-        <v>964</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B942" t="s">
-        <v>1839</v>
+        <v>966</v>
       </c>
     </row>
     <row r="943" spans="1:2">
@@ -15115,12 +15115,12 @@
         <v>1904</v>
       </c>
       <c r="B975" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B976" t="s">
         <v>1906</v>
@@ -15131,12 +15131,12 @@
         <v>1907</v>
       </c>
       <c r="B977" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B978" t="s">
         <v>1909</v>
@@ -15259,15 +15259,15 @@
         <v>1938</v>
       </c>
       <c r="B993" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B994" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="995" spans="1:2">
@@ -15379,15 +15379,15 @@
         <v>1967</v>
       </c>
       <c r="B1008" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1009" t="s">
         <v>1968</v>
-      </c>
-      <c r="B1009" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
@@ -15427,15 +15427,15 @@
         <v>1978</v>
       </c>
       <c r="B1014" t="s">
-        <v>255</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1015" t="s">
-        <v>1980</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
@@ -15531,12 +15531,12 @@
         <v>2003</v>
       </c>
       <c r="B1027" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B1028" t="s">
         <v>2005</v>
@@ -15611,12 +15611,12 @@
         <v>2022</v>
       </c>
       <c r="B1037" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B1038" t="s">
         <v>2024</v>
@@ -16059,15 +16059,15 @@
         <v>2133</v>
       </c>
       <c r="B1093" t="s">
-        <v>527</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B1094" t="s">
-        <v>2135</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
@@ -16139,15 +16139,15 @@
         <v>2152</v>
       </c>
       <c r="B1103" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2153</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
@@ -16283,12 +16283,12 @@
         <v>2187</v>
       </c>
       <c r="B1121" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="B1122" t="s">
         <v>2189</v>
@@ -16299,12 +16299,12 @@
         <v>2190</v>
       </c>
       <c r="B1123" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="B1124" t="s">
         <v>2192</v>
@@ -16499,15 +16499,15 @@
         <v>2239</v>
       </c>
       <c r="B1148" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2240</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
@@ -16523,12 +16523,12 @@
         <v>2244</v>
       </c>
       <c r="B1151" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="B1152" t="s">
         <v>2246</v>
@@ -16667,20 +16667,20 @@
         <v>2279</v>
       </c>
       <c r="B1169" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B1170" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="B1171" t="s">
         <v>2282</v>
@@ -16691,12 +16691,12 @@
         <v>2283</v>
       </c>
       <c r="B1172" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B1173" t="s">
         <v>2285</v>
@@ -16723,12 +16723,12 @@
         <v>2290</v>
       </c>
       <c r="B1176" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="B1177" t="s">
         <v>2292</v>
@@ -16739,12 +16739,12 @@
         <v>2293</v>
       </c>
       <c r="B1178" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="B1179" t="s">
         <v>2295</v>
@@ -16803,23 +16803,23 @@
         <v>2308</v>
       </c>
       <c r="B1186" t="s">
-        <v>68</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="B1187" t="s">
-        <v>2172</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="B1188" t="s">
-        <v>2311</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1189" spans="1:2">

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2318">
   <si>
     <t>en</t>
   </si>
@@ -5168,6 +5168,12 @@
   </si>
   <si>
     <t>掠食者</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>史前生物</t>
   </si>
   <si>
     <t>Present</t>
@@ -7311,7 +7317,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14427,12 +14433,12 @@
         <v>1737</v>
       </c>
       <c r="B889" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B890" t="s">
         <v>1739</v>
@@ -14475,12 +14481,12 @@
         <v>1748</v>
       </c>
       <c r="B895" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B896" t="s">
         <v>1750</v>
@@ -14715,20 +14721,20 @@
         <v>1807</v>
       </c>
       <c r="B925" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B926" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B927" t="s">
         <v>1810</v>
@@ -14851,15 +14857,15 @@
         <v>1839</v>
       </c>
       <c r="B942" t="s">
-        <v>966</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B943" t="s">
-        <v>1841</v>
+        <v>966</v>
       </c>
     </row>
     <row r="944" spans="1:2">
@@ -15123,12 +15129,12 @@
         <v>1906</v>
       </c>
       <c r="B976" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B977" t="s">
         <v>1908</v>
@@ -15139,12 +15145,12 @@
         <v>1909</v>
       </c>
       <c r="B978" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B979" t="s">
         <v>1911</v>
@@ -15267,15 +15273,15 @@
         <v>1940</v>
       </c>
       <c r="B994" t="s">
-        <v>1935</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B995" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="996" spans="1:2">
@@ -15387,15 +15393,15 @@
         <v>1969</v>
       </c>
       <c r="B1009" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1970</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
@@ -15435,15 +15441,15 @@
         <v>1980</v>
       </c>
       <c r="B1015" t="s">
-        <v>255</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1016" t="s">
-        <v>1982</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
@@ -15539,12 +15545,12 @@
         <v>2005</v>
       </c>
       <c r="B1028" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B1029" t="s">
         <v>2007</v>
@@ -15619,12 +15625,12 @@
         <v>2024</v>
       </c>
       <c r="B1038" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1039" t="s">
         <v>2026</v>
@@ -16067,15 +16073,15 @@
         <v>2135</v>
       </c>
       <c r="B1094" t="s">
-        <v>527</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B1095" t="s">
-        <v>2137</v>
+        <v>527</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
@@ -16147,15 +16153,15 @@
         <v>2154</v>
       </c>
       <c r="B1104" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2155</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
@@ -16291,12 +16297,12 @@
         <v>2189</v>
       </c>
       <c r="B1122" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B1123" t="s">
         <v>2191</v>
@@ -16307,12 +16313,12 @@
         <v>2192</v>
       </c>
       <c r="B1124" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="B1125" t="s">
         <v>2194</v>
@@ -16507,15 +16513,15 @@
         <v>2241</v>
       </c>
       <c r="B1149" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2242</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
@@ -16531,12 +16537,12 @@
         <v>2246</v>
       </c>
       <c r="B1152" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="B1153" t="s">
         <v>2248</v>
@@ -16675,20 +16681,20 @@
         <v>2281</v>
       </c>
       <c r="B1170" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B1171" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="B1172" t="s">
         <v>2284</v>
@@ -16699,12 +16705,12 @@
         <v>2285</v>
       </c>
       <c r="B1173" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="B1174" t="s">
         <v>2287</v>
@@ -16731,12 +16737,12 @@
         <v>2292</v>
       </c>
       <c r="B1177" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="B1178" t="s">
         <v>2294</v>
@@ -16747,12 +16753,12 @@
         <v>2295</v>
       </c>
       <c r="B1179" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="B1180" t="s">
         <v>2297</v>
@@ -16811,23 +16817,23 @@
         <v>2310</v>
       </c>
       <c r="B1187" t="s">
-        <v>68</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="B1188" t="s">
-        <v>2174</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="B1189" t="s">
-        <v>2313</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
@@ -16838,8 +16844,16 @@
         <v>2315</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2317</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2320">
   <si>
     <t>en</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>回到未来</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>《Backrooms》（电影）</t>
   </si>
   <si>
     <t>Bag</t>
@@ -7317,7 +7323,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7873,12 +7879,12 @@
         <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
         <v>135</v>
@@ -8009,12 +8015,12 @@
         <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
         <v>168</v>
@@ -8169,12 +8175,12 @@
         <v>205</v>
       </c>
       <c r="B106" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B107" t="s">
         <v>207</v>
@@ -8185,12 +8191,12 @@
         <v>208</v>
       </c>
       <c r="B108" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B109" t="s">
         <v>210</v>
@@ -8225,15 +8231,15 @@
         <v>217</v>
       </c>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
+        <v>219</v>
+      </c>
+      <c r="B114" t="s">
         <v>218</v>
-      </c>
-      <c r="B114" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8425,15 +8431,15 @@
         <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>268</v>
+      </c>
+      <c r="B139" t="s">
         <v>267</v>
-      </c>
-      <c r="B139" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8945,15 +8951,15 @@
         <v>395</v>
       </c>
       <c r="B203" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B204" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -9177,12 +9183,12 @@
         <v>452</v>
       </c>
       <c r="B232" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B233" t="s">
         <v>454</v>
@@ -9377,15 +9383,15 @@
         <v>501</v>
       </c>
       <c r="B257" t="s">
-        <v>204</v>
+        <v>502</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B258" t="s">
-        <v>503</v>
+        <v>206</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9697,15 +9703,15 @@
         <v>580</v>
       </c>
       <c r="B297" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B298" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -9881,12 +9887,12 @@
         <v>625</v>
       </c>
       <c r="B320" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B321" t="s">
         <v>627</v>
@@ -9985,12 +9991,12 @@
         <v>650</v>
       </c>
       <c r="B333" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B334" t="s">
         <v>652</v>
@@ -11065,20 +11071,20 @@
         <v>919</v>
       </c>
       <c r="B468" t="s">
-        <v>624</v>
+        <v>920</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B469" t="s">
-        <v>920</v>
+        <v>626</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B470" t="s">
         <v>922</v>
@@ -11305,15 +11311,15 @@
         <v>977</v>
       </c>
       <c r="B498" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B499" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -11513,15 +11519,15 @@
         <v>1028</v>
       </c>
       <c r="B524" t="s">
-        <v>282</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B525" t="s">
-        <v>1030</v>
+        <v>284</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -11561,15 +11567,15 @@
         <v>1039</v>
       </c>
       <c r="B530" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B531" t="s">
         <v>1040</v>
-      </c>
-      <c r="B531" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -11745,28 +11751,28 @@
         <v>1084</v>
       </c>
       <c r="B553" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B554" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B555" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B556" t="s">
         <v>1088</v>
@@ -11777,12 +11783,12 @@
         <v>1089</v>
       </c>
       <c r="B557" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B558" t="s">
         <v>1091</v>
@@ -11977,12 +11983,12 @@
         <v>1138</v>
       </c>
       <c r="B582" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B583" t="s">
         <v>1140</v>
@@ -12121,12 +12127,12 @@
         <v>1173</v>
       </c>
       <c r="B600" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B601" t="s">
         <v>1175</v>
@@ -12449,12 +12455,12 @@
         <v>1254</v>
       </c>
       <c r="B641" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B642" t="s">
         <v>1256</v>
@@ -13681,12 +13687,12 @@
         <v>1561</v>
       </c>
       <c r="B795" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B796" t="s">
         <v>1563</v>
@@ -13713,15 +13719,15 @@
         <v>1568</v>
       </c>
       <c r="B799" t="s">
-        <v>966</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B800" t="s">
-        <v>1570</v>
+        <v>968</v>
       </c>
     </row>
     <row r="801" spans="1:2">
@@ -13729,20 +13735,20 @@
         <v>1571</v>
       </c>
       <c r="B801" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B802" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B803" t="s">
         <v>1574</v>
@@ -13761,20 +13767,20 @@
         <v>1577</v>
       </c>
       <c r="B805" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B806" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B807" t="s">
         <v>1580</v>
@@ -14073,15 +14079,15 @@
         <v>1653</v>
       </c>
       <c r="B844" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B845" t="s">
         <v>1654</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="846" spans="1:2">
@@ -14137,23 +14143,23 @@
         <v>1668</v>
       </c>
       <c r="B852" t="s">
-        <v>1620</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B853" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B854" t="s">
-        <v>1671</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="855" spans="1:2">
@@ -14289,28 +14295,28 @@
         <v>1704</v>
       </c>
       <c r="B871" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B872" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B873" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B874" t="s">
         <v>1708</v>
@@ -14441,12 +14447,12 @@
         <v>1739</v>
       </c>
       <c r="B890" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B891" t="s">
         <v>1741</v>
@@ -14489,12 +14495,12 @@
         <v>1750</v>
       </c>
       <c r="B896" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B897" t="s">
         <v>1752</v>
@@ -14729,20 +14735,20 @@
         <v>1809</v>
       </c>
       <c r="B926" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B927" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B928" t="s">
         <v>1812</v>
@@ -14865,15 +14871,15 @@
         <v>1841</v>
       </c>
       <c r="B943" t="s">
-        <v>966</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B944" t="s">
-        <v>1843</v>
+        <v>968</v>
       </c>
     </row>
     <row r="945" spans="1:2">
@@ -15137,12 +15143,12 @@
         <v>1908</v>
       </c>
       <c r="B977" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B978" t="s">
         <v>1910</v>
@@ -15153,12 +15159,12 @@
         <v>1911</v>
       </c>
       <c r="B979" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B980" t="s">
         <v>1913</v>
@@ -15281,15 +15287,15 @@
         <v>1942</v>
       </c>
       <c r="B995" t="s">
-        <v>1937</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B996" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="997" spans="1:2">
@@ -15401,15 +15407,15 @@
         <v>1971</v>
       </c>
       <c r="B1010" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1011" t="s">
         <v>1972</v>
-      </c>
-      <c r="B1011" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
@@ -15449,15 +15455,15 @@
         <v>1982</v>
       </c>
       <c r="B1016" t="s">
-        <v>255</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1017" t="s">
-        <v>1984</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
@@ -15553,12 +15559,12 @@
         <v>2007</v>
       </c>
       <c r="B1029" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B1030" t="s">
         <v>2009</v>
@@ -15633,12 +15639,12 @@
         <v>2026</v>
       </c>
       <c r="B1039" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1040" t="s">
         <v>2028</v>
@@ -16081,15 +16087,15 @@
         <v>2137</v>
       </c>
       <c r="B1095" t="s">
-        <v>527</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="B1096" t="s">
-        <v>2139</v>
+        <v>529</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
@@ -16161,15 +16167,15 @@
         <v>2156</v>
       </c>
       <c r="B1105" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1106" t="s">
         <v>2157</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>2158</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
@@ -16305,12 +16311,12 @@
         <v>2191</v>
       </c>
       <c r="B1123" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B1124" t="s">
         <v>2193</v>
@@ -16321,12 +16327,12 @@
         <v>2194</v>
       </c>
       <c r="B1125" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B1126" t="s">
         <v>2196</v>
@@ -16521,15 +16527,15 @@
         <v>2243</v>
       </c>
       <c r="B1150" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2244</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
@@ -16545,12 +16551,12 @@
         <v>2248</v>
       </c>
       <c r="B1153" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="B1154" t="s">
         <v>2250</v>
@@ -16689,20 +16695,20 @@
         <v>2283</v>
       </c>
       <c r="B1171" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B1172" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="B1173" t="s">
         <v>2286</v>
@@ -16713,12 +16719,12 @@
         <v>2287</v>
       </c>
       <c r="B1174" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B1175" t="s">
         <v>2289</v>
@@ -16745,12 +16751,12 @@
         <v>2294</v>
       </c>
       <c r="B1178" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="B1179" t="s">
         <v>2296</v>
@@ -16761,12 +16767,12 @@
         <v>2297</v>
       </c>
       <c r="B1180" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="B1181" t="s">
         <v>2299</v>
@@ -16825,23 +16831,23 @@
         <v>2312</v>
       </c>
       <c r="B1188" t="s">
-        <v>68</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="B1189" t="s">
-        <v>2176</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="B1190" t="s">
-        <v>2315</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
@@ -16852,8 +16858,16 @@
         <v>2317</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2319</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2322">
   <si>
     <t>en</t>
   </si>
@@ -1514,6 +1514,12 @@
   </si>
   <si>
     <t>暗黑破坏神</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>死亡之骰</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -7323,7 +7329,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9391,15 +9397,15 @@
         <v>503</v>
       </c>
       <c r="B258" t="s">
-        <v>206</v>
+        <v>504</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B259" t="s">
-        <v>505</v>
+        <v>206</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9711,15 +9717,15 @@
         <v>582</v>
       </c>
       <c r="B298" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B299" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -9895,12 +9901,12 @@
         <v>627</v>
       </c>
       <c r="B321" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B322" t="s">
         <v>629</v>
@@ -9999,12 +10005,12 @@
         <v>652</v>
       </c>
       <c r="B334" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B335" t="s">
         <v>654</v>
@@ -11079,20 +11085,20 @@
         <v>921</v>
       </c>
       <c r="B469" t="s">
-        <v>626</v>
+        <v>922</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B470" t="s">
-        <v>922</v>
+        <v>628</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B471" t="s">
         <v>924</v>
@@ -11319,15 +11325,15 @@
         <v>979</v>
       </c>
       <c r="B499" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B500" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -11527,15 +11533,15 @@
         <v>1030</v>
       </c>
       <c r="B525" t="s">
-        <v>284</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B526" t="s">
-        <v>1032</v>
+        <v>284</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -11575,15 +11581,15 @@
         <v>1041</v>
       </c>
       <c r="B531" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B532" t="s">
         <v>1042</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -11759,28 +11765,28 @@
         <v>1086</v>
       </c>
       <c r="B554" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B555" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B556" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B557" t="s">
         <v>1090</v>
@@ -11791,12 +11797,12 @@
         <v>1091</v>
       </c>
       <c r="B558" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B559" t="s">
         <v>1093</v>
@@ -11991,12 +11997,12 @@
         <v>1140</v>
       </c>
       <c r="B583" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B584" t="s">
         <v>1142</v>
@@ -12135,12 +12141,12 @@
         <v>1175</v>
       </c>
       <c r="B601" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B602" t="s">
         <v>1177</v>
@@ -12463,12 +12469,12 @@
         <v>1256</v>
       </c>
       <c r="B642" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B643" t="s">
         <v>1258</v>
@@ -13695,12 +13701,12 @@
         <v>1563</v>
       </c>
       <c r="B796" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B797" t="s">
         <v>1565</v>
@@ -13727,15 +13733,15 @@
         <v>1570</v>
       </c>
       <c r="B800" t="s">
-        <v>968</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B801" t="s">
-        <v>1572</v>
+        <v>970</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -13743,20 +13749,20 @@
         <v>1573</v>
       </c>
       <c r="B802" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B803" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B804" t="s">
         <v>1576</v>
@@ -13775,20 +13781,20 @@
         <v>1579</v>
       </c>
       <c r="B806" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B807" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B808" t="s">
         <v>1582</v>
@@ -14087,15 +14093,15 @@
         <v>1655</v>
       </c>
       <c r="B845" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B846" t="s">
         <v>1656</v>
-      </c>
-      <c r="B846" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="847" spans="1:2">
@@ -14151,23 +14157,23 @@
         <v>1670</v>
       </c>
       <c r="B853" t="s">
-        <v>1622</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B854" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B855" t="s">
-        <v>1673</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="856" spans="1:2">
@@ -14303,28 +14309,28 @@
         <v>1706</v>
       </c>
       <c r="B872" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B873" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B874" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B875" t="s">
         <v>1710</v>
@@ -14455,12 +14461,12 @@
         <v>1741</v>
       </c>
       <c r="B891" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B892" t="s">
         <v>1743</v>
@@ -14503,12 +14509,12 @@
         <v>1752</v>
       </c>
       <c r="B897" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B898" t="s">
         <v>1754</v>
@@ -14743,20 +14749,20 @@
         <v>1811</v>
       </c>
       <c r="B927" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B928" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B929" t="s">
         <v>1814</v>
@@ -14879,15 +14885,15 @@
         <v>1843</v>
       </c>
       <c r="B944" t="s">
-        <v>968</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B945" t="s">
-        <v>1845</v>
+        <v>970</v>
       </c>
     </row>
     <row r="946" spans="1:2">
@@ -15151,12 +15157,12 @@
         <v>1910</v>
       </c>
       <c r="B978" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B979" t="s">
         <v>1912</v>
@@ -15167,12 +15173,12 @@
         <v>1913</v>
       </c>
       <c r="B980" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B981" t="s">
         <v>1915</v>
@@ -15295,15 +15301,15 @@
         <v>1944</v>
       </c>
       <c r="B996" t="s">
-        <v>1939</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B997" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="998" spans="1:2">
@@ -15415,15 +15421,15 @@
         <v>1973</v>
       </c>
       <c r="B1011" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1974</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
@@ -15463,15 +15469,15 @@
         <v>1984</v>
       </c>
       <c r="B1017" t="s">
-        <v>257</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1018" t="s">
-        <v>1986</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
@@ -15567,12 +15573,12 @@
         <v>2009</v>
       </c>
       <c r="B1030" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B1031" t="s">
         <v>2011</v>
@@ -15647,12 +15653,12 @@
         <v>2028</v>
       </c>
       <c r="B1040" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1041" t="s">
         <v>2030</v>
@@ -16095,15 +16101,15 @@
         <v>2139</v>
       </c>
       <c r="B1096" t="s">
-        <v>529</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B1097" t="s">
-        <v>2141</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
@@ -16175,15 +16181,15 @@
         <v>2158</v>
       </c>
       <c r="B1106" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2159</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
@@ -16319,12 +16325,12 @@
         <v>2193</v>
       </c>
       <c r="B1124" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B1125" t="s">
         <v>2195</v>
@@ -16335,12 +16341,12 @@
         <v>2196</v>
       </c>
       <c r="B1126" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="B1127" t="s">
         <v>2198</v>
@@ -16535,15 +16541,15 @@
         <v>2245</v>
       </c>
       <c r="B1151" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2246</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
@@ -16559,12 +16565,12 @@
         <v>2250</v>
       </c>
       <c r="B1154" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="B1155" t="s">
         <v>2252</v>
@@ -16703,20 +16709,20 @@
         <v>2285</v>
       </c>
       <c r="B1172" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="B1173" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="B1174" t="s">
         <v>2288</v>
@@ -16727,12 +16733,12 @@
         <v>2289</v>
       </c>
       <c r="B1175" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B1176" t="s">
         <v>2291</v>
@@ -16759,12 +16765,12 @@
         <v>2296</v>
       </c>
       <c r="B1179" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="B1180" t="s">
         <v>2298</v>
@@ -16775,12 +16781,12 @@
         <v>2299</v>
       </c>
       <c r="B1181" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="B1182" t="s">
         <v>2301</v>
@@ -16839,23 +16845,23 @@
         <v>2314</v>
       </c>
       <c r="B1189" t="s">
-        <v>68</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="B1190" t="s">
-        <v>2178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="B1191" t="s">
-        <v>2317</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
@@ -16866,8 +16872,16 @@
         <v>2319</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2321</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/zh/headTags.xlsx
+++ b/lang/zh/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2324">
   <si>
     <t>en</t>
   </si>
@@ -2456,6 +2456,12 @@
   </si>
   <si>
     <t>字体（橙色）</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>字体（浅橡木）</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -7329,7 +7335,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1193"/>
+  <dimension ref="A1:B1194"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11093,20 +11099,20 @@
         <v>923</v>
       </c>
       <c r="B470" t="s">
-        <v>628</v>
+        <v>924</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B471" t="s">
-        <v>924</v>
+        <v>628</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B472" t="s">
         <v>926</v>
@@ -11333,15 +11339,15 @@
         <v>981</v>
       </c>
       <c r="B500" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B501" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -11541,15 +11547,15 @@
         <v>1032</v>
       </c>
       <c r="B526" t="s">
-        <v>284</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B527" t="s">
-        <v>1034</v>
+        <v>284</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -11589,15 +11595,15 @@
         <v>1043</v>
       </c>
       <c r="B532" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B533" t="s">
         <v>1044</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -11773,28 +11779,28 @@
         <v>1088</v>
       </c>
       <c r="B555" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B556" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B557" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B558" t="s">
         <v>1092</v>
@@ -11805,12 +11811,12 @@
         <v>1093</v>
       </c>
       <c r="B559" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B560" t="s">
         <v>1095</v>
@@ -12005,12 +12011,12 @@
         <v>1142</v>
       </c>
       <c r="B584" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B585" t="s">
         <v>1144</v>
@@ -12149,12 +12155,12 @@
         <v>1177</v>
       </c>
       <c r="B602" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B603" t="s">
         <v>1179</v>
@@ -12477,12 +12483,12 @@
         <v>1258</v>
       </c>
       <c r="B643" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B644" t="s">
         <v>1260</v>
@@ -13709,12 +13715,12 @@
         <v>1565</v>
       </c>
       <c r="B797" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B798" t="s">
         <v>1567</v>
@@ -13741,15 +13747,15 @@
         <v>1572</v>
       </c>
       <c r="B801" t="s">
-        <v>970</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B802" t="s">
-        <v>1574</v>
+        <v>972</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -13757,20 +13763,20 @@
         <v>1575</v>
       </c>
       <c r="B803" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B804" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B805" t="s">
         <v>1578</v>
@@ -13789,20 +13795,20 @@
         <v>1581</v>
       </c>
       <c r="B807" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B808" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B809" t="s">
         <v>1584</v>
@@ -14101,15 +14107,15 @@
         <v>1657</v>
       </c>
       <c r="B846" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B847" t="s">
         <v>1658</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="848" spans="1:2">
@@ -14165,23 +14171,23 @@
         <v>1672</v>
       </c>
       <c r="B854" t="s">
-        <v>1624</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B855" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B856" t="s">
-        <v>1675</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="857" spans="1:2">
@@ -14317,28 +14323,28 @@
         <v>1708</v>
       </c>
       <c r="B873" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B874" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B875" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B876" t="s">
         <v>1712</v>
@@ -14469,12 +14475,12 @@
         <v>1743</v>
       </c>
       <c r="B892" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B893" t="s">
         <v>1745</v>
@@ -14517,12 +14523,12 @@
         <v>1754</v>
       </c>
       <c r="B898" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B899" t="s">
         <v>1756</v>
@@ -14757,20 +14763,20 @@
         <v>1813</v>
       </c>
       <c r="B928" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B929" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B930" t="s">
         <v>1816</v>
@@ -14893,15 +14899,15 @@
         <v>1845</v>
       </c>
       <c r="B945" t="s">
-        <v>970</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B946" t="s">
-        <v>1847</v>
+        <v>972</v>
       </c>
     </row>
     <row r="947" spans="1:2">
@@ -15165,12 +15171,12 @@
         <v>1912</v>
       </c>
       <c r="B979" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B980" t="s">
         <v>1914</v>
@@ -15181,12 +15187,12 @@
         <v>1915</v>
       </c>
       <c r="B981" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B982" t="s">
         <v>1917</v>
@@ -15309,15 +15315,15 @@
         <v>1946</v>
       </c>
       <c r="B997" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B998" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="999" spans="1:2">
@@ -15429,15 +15435,15 @@
         <v>1975</v>
       </c>
       <c r="B1012" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1976</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
@@ -15477,15 +15483,15 @@
         <v>1986</v>
       </c>
       <c r="B1018" t="s">
-        <v>257</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1019" t="s">
-        <v>1988</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
@@ -15581,12 +15587,12 @@
         <v>2011</v>
       </c>
       <c r="B1031" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B1032" t="s">
         <v>2013</v>
@@ -15661,12 +15667,12 @@
         <v>2030</v>
       </c>
       <c r="B1041" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1042" t="s">
         <v>2032</v>
@@ -16109,15 +16115,15 @@
         <v>2141</v>
       </c>
       <c r="B1097" t="s">
-        <v>531</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="B1098" t="s">
-        <v>2143</v>
+        <v>531</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
@@ -16189,15 +16195,15 @@
         <v>2160</v>
       </c>
       <c r="B1107" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2161</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
@@ -16333,12 +16339,12 @@
         <v>2195</v>
       </c>
       <c r="B1125" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B1126" t="s">
         <v>2197</v>
@@ -16349,12 +16355,12 @@
         <v>2198</v>
       </c>
       <c r="B1127" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B1128" t="s">
         <v>2200</v>
@@ -16549,15 +16555,15 @@
         <v>2247</v>
       </c>
       <c r="B1152" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2248</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
@@ -16573,12 +16579,12 @@
         <v>2252</v>
       </c>
       <c r="B1155" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="B1156" t="s">
         <v>2254</v>
@@ -16717,20 +16723,20 @@
         <v>2287</v>
       </c>
       <c r="B1173" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B1174" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B1175" t="s">
         <v>2290</v>
@@ -16741,12 +16747,12 @@
         <v>2291</v>
       </c>
       <c r="B1176" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="B1177" t="s">
         <v>2293</v>
@@ -16773,12 +16779,12 @@
         <v>2298</v>
       </c>
       <c r="B1180" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="B1181" t="s">
         <v>2300</v>
@@ -16789,12 +16795,12 @@
         <v>2301</v>
       </c>
       <c r="B1182" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="B1183" t="s">
         <v>2303</v>
@@ -16853,23 +16859,23 @@
         <v>2316</v>
       </c>
       <c r="B1190" t="s">
-        <v>68</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="B1191" t="s">
-        <v>2180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="B1192" t="s">
-        <v>2319</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
@@ -16880,8 +16886,16 @@
         <v>2321</v>
       </c>
     </row>
+    <row r="1194" spans="1:2">
+      <c r="A1194" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>2323</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1193"/>
+  <autoFilter ref="A1:B1194"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
